--- a/restaurant_crawler/restaurant_data_台北_燒肉_20250910_192607_with_emails.xlsx
+++ b/restaurant_crawler/restaurant_data_台北_燒肉_20250910_192607_with_emails.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\slow3\OneDrive\桌面\GitHubProjects\BYOB\restaurant_crawler\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{30BF8F39-1C0B-443E-B081-7ED2BD14A136}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C4BA7C91-1649-4F18-8DF3-A1D4B3D49D34}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="370" uniqueCount="307">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="209" uniqueCount="180">
   <si>
     <t>name</t>
   </si>
@@ -199,51 +199,6 @@
     <t>ChIJTeglZsWrQjQR_E437fbm3QI</t>
   </si>
   <si>
-    <t>豆町村燒肉</t>
-  </si>
-  <si>
-    <t>10696台灣台北市大安區延吉街131巷27號1樓</t>
-  </si>
-  <si>
-    <t>02 8771 0380</t>
-  </si>
-  <si>
-    <t>https://lin.ee/hTl7Zyq</t>
-  </si>
-  <si>
-    <t>ChIJz6YB9QirQjQRZQNP7V47Op0</t>
-  </si>
-  <si>
-    <t>八和和牛燒肉專門店-安和本店</t>
-  </si>
-  <si>
-    <t>106台灣台北市大安區安和路一段102巷4號</t>
-  </si>
-  <si>
-    <t>02 2325 0531</t>
-  </si>
-  <si>
-    <t>https://reurl.cc/Y8blDl</t>
-  </si>
-  <si>
-    <t>ChIJE1LImuCrQjQRGSzP6ydyfZM</t>
-  </si>
-  <si>
-    <t>山上走走 日式燒肉台北華山店</t>
-  </si>
-  <si>
-    <t>100台灣台北市中正區金山南路一段8號</t>
-  </si>
-  <si>
-    <t>02 2397 1777</t>
-  </si>
-  <si>
-    <t>https://inline.app/booking/-Ll6KebqTaG9qa0eLrqY:inline-live-1/-NXV5pScQif96V_2MTAv?fbclid=IwAR19HmHXftFj1cpSA261VHQWE3QVxGXAQn_fV8rpceihdqVrZOtx__iUslM</t>
-  </si>
-  <si>
-    <t>ChIJJ1Hcl7OpQjQR3Aj7-220DyA</t>
-  </si>
-  <si>
     <t>燒肉中山｜台北信義</t>
   </si>
   <si>
@@ -289,48 +244,6 @@
     <t>ChIJbW3iLtCrQjQRD7Ci4t5cbKU</t>
   </si>
   <si>
-    <t>久碳吉炭火燒肉</t>
-  </si>
-  <si>
-    <t>106台灣台北市大安區延吉街72-8號</t>
-  </si>
-  <si>
-    <t>0963 659 091</t>
-  </si>
-  <si>
-    <t>https://iiil.io/jzPm</t>
-  </si>
-  <si>
-    <t>ChIJXbHvJcarQjQRRitxXggdN8U</t>
-  </si>
-  <si>
-    <t>燒肉政宗</t>
-  </si>
-  <si>
-    <t>106台灣台北市大安區忠孝東路四段101巷7號</t>
-  </si>
-  <si>
-    <t>02 2771 8007</t>
-  </si>
-  <si>
-    <t>https://inline.app/booking/-NW0wVz88vneBilAg9zA:inline-live-3?language=zh-tw</t>
-  </si>
-  <si>
-    <t>ChIJNR1pKRWrQjQRdJxVoSQTBm4</t>
-  </si>
-  <si>
-    <t>大阪燒肉 燒魂Yakikon大安本店</t>
-  </si>
-  <si>
-    <t>106台灣台北市大安區大安路一段19巷3號</t>
-  </si>
-  <si>
-    <t>02 2775 3614</t>
-  </si>
-  <si>
-    <t>ChIJ0X9pW9qrQjQRVcWAoUfGunA</t>
-  </si>
-  <si>
     <t>燒肉眾精緻炭火燒肉 台北西門店</t>
   </si>
   <si>
@@ -349,57 +262,6 @@
     <t>example@gmail.com</t>
   </si>
   <si>
-    <t>Yakiniku燒肉</t>
-  </si>
-  <si>
-    <t>106台灣台北市大安區敦化南路一段169巷7號</t>
-  </si>
-  <si>
-    <t>ChIJA7vwpICrQjQR6YWZZ4uzQJY</t>
-  </si>
-  <si>
-    <t>IKIGAI燒肉專門店 三越A8店</t>
-  </si>
-  <si>
-    <t>B1, No. 12號松高路信義區台北市台灣 110</t>
-  </si>
-  <si>
-    <t>02 8789 1079</t>
-  </si>
-  <si>
-    <t>ChIJ2zHgVACrQjQRmrxHydUz9SE</t>
-  </si>
-  <si>
-    <t>初樂燒肉 東區大安店 燒烤 BBQ 忠孝復興</t>
-  </si>
-  <si>
-    <t>106台灣台北市大安區敦化南路一段190巷42號</t>
-  </si>
-  <si>
-    <t>0908 175 888</t>
-  </si>
-  <si>
-    <t>http://instagram.com/truefun_fun</t>
-  </si>
-  <si>
-    <t>ChIJm4jTXbqrQjQRxzNzJeJnZdE</t>
-  </si>
-  <si>
-    <t>肉你好燒肉-延吉店</t>
-  </si>
-  <si>
-    <t>106台灣台北市大安區延吉街160巷11號1樓</t>
-  </si>
-  <si>
-    <t>0928 210 510</t>
-  </si>
-  <si>
-    <t>https://linktr.ee/yoloniku</t>
-  </si>
-  <si>
-    <t>ChIJq5Kx4oOrQjQR4_IjXH9uSA8</t>
-  </si>
-  <si>
     <t>赤富士日式燒肉鍋物-西門店</t>
   </si>
   <si>
@@ -448,21 +310,6 @@
     <t>ChIJr4OO6PKrQjQRrbMx8Y35umQ</t>
   </si>
   <si>
-    <t>青杉燒肉</t>
-  </si>
-  <si>
-    <t>106台灣台北市大安區仁愛路四段345巷4弄8號</t>
-  </si>
-  <si>
-    <t>0984 189 958</t>
-  </si>
-  <si>
-    <t>https://instagram.com/aosugi.yakiniku</t>
-  </si>
-  <si>
-    <t>ChIJ0T4eQzarQjQRg74zdaclK2o</t>
-  </si>
-  <si>
     <t>燒肉PUNCH3號店┃燔太師東區預備店</t>
   </si>
   <si>
@@ -478,33 +325,6 @@
     <t>ChIJJ8iY-rCrQjQRXasrLM4eMfo</t>
   </si>
   <si>
-    <t>焼肉スマイル（燒肉Smile）台北忠孝店</t>
-  </si>
-  <si>
-    <t>110台灣台北市信義區忠孝東路五段497號2樓</t>
-  </si>
-  <si>
-    <t>02 8785 2227</t>
-  </si>
-  <si>
-    <t>https://linktr.ee/yakinikusmile</t>
-  </si>
-  <si>
-    <t>ChIJqdWHeL-rQjQRN-J5jXwWH6Y</t>
-  </si>
-  <si>
-    <t>焼肉スマイル（燒肉Smile）大安忠孝店(自助吧)</t>
-  </si>
-  <si>
-    <t>106台灣台北市大安區忠孝東路四段104號2樓之1</t>
-  </si>
-  <si>
-    <t>02 2752 2000</t>
-  </si>
-  <si>
-    <t>ChIJP2dhm92rQjQRMAPRTp3UTK8</t>
-  </si>
-  <si>
     <t>揪餖燒肉 微風南山店</t>
   </si>
   <si>
@@ -523,33 +343,6 @@
     <t>haoke3838@gmail.com</t>
   </si>
   <si>
-    <t>燒肉神保町信義館</t>
-  </si>
-  <si>
-    <t>110台灣台北市信義區松壽路12號4樓</t>
-  </si>
-  <si>
-    <t>02 7735 2868</t>
-  </si>
-  <si>
-    <t>ChIJcWEmupOrQjQR9z8BvRI1cW0</t>
-  </si>
-  <si>
-    <t>胖肚肚燒肉 京華店</t>
-  </si>
-  <si>
-    <t>105台灣台北市松山區八德路四段108號2樓</t>
-  </si>
-  <si>
-    <t>02 2760 1909</t>
-  </si>
-  <si>
-    <t>https://pundodo.com/</t>
-  </si>
-  <si>
-    <t>ChIJR4abX5WrQjQRTMaNABDKaSY</t>
-  </si>
-  <si>
     <t>樂軒松阪亭</t>
   </si>
   <si>
@@ -565,30 +358,6 @@
     <t>ChIJL6olmHSrQjQRLQ7itONyGgs</t>
   </si>
   <si>
-    <t>肉你好燒肉-合江總舖</t>
-  </si>
-  <si>
-    <t>104台灣台北市中山區合江街178號</t>
-  </si>
-  <si>
-    <t>0928 926 661</t>
-  </si>
-  <si>
-    <t>ChIJcTd2UOKrQjQRkEDS5eu1X_c</t>
-  </si>
-  <si>
-    <t>肉你好燒肉-南京三民店</t>
-  </si>
-  <si>
-    <t>105台灣台北市松山區南京東路五段53-1號</t>
-  </si>
-  <si>
-    <t>0928 925 551</t>
-  </si>
-  <si>
-    <t>ChIJJ37zOkKrQjQRBcrNlL-8gSA</t>
-  </si>
-  <si>
     <t>赤身燒肉 USHIO Taipei</t>
   </si>
   <si>
@@ -634,9 +403,6 @@
     <t>02 8941 9966</t>
   </si>
   <si>
-    <t>https://rink.cc/u0ddp</t>
-  </si>
-  <si>
     <t>ChIJwcdwcFgDaDQRrGlEsHdHYFw</t>
   </si>
   <si>
@@ -670,33 +436,6 @@
     <t>ChIJ4bCwiy6rQjQRJUxidbgF2ow</t>
   </si>
   <si>
-    <t>八和和牛燒肉專門店 敦北二號店</t>
-  </si>
-  <si>
-    <t>10547台灣台北市松山區敦化北路100號</t>
-  </si>
-  <si>
-    <t>02 2712 3442</t>
-  </si>
-  <si>
-    <t>https://reurl.cc/5MyRkz</t>
-  </si>
-  <si>
-    <t>ChIJOw7k4y6rQjQRyc4JtlLbAkQ</t>
-  </si>
-  <si>
-    <t>蘭亭燒肉 和牛極緻料理</t>
-  </si>
-  <si>
-    <t>106台灣台北市大安區四維路52巷12號</t>
-  </si>
-  <si>
-    <t>02 2703 0285</t>
-  </si>
-  <si>
-    <t>ChIJaX43PdKrQjQRpihORwmRBY8</t>
-  </si>
-  <si>
     <t>小滿苑燒肉</t>
   </si>
   <si>
@@ -712,36 +451,6 @@
     <t>ChIJy7EokcarQjQRJJj8f8Cmfhc</t>
   </si>
   <si>
-    <t>路易奇電力公司 中山第一電廠</t>
-  </si>
-  <si>
-    <t>104台灣台北市中山區中山北路一段83巷9之5號1樓</t>
-  </si>
-  <si>
-    <t>02 2568 1031</t>
-  </si>
-  <si>
-    <t>https://inline.app/booking/-NGLeeWVrO75oy6CHhRk:inline-live-3?language=zh-tw</t>
-  </si>
-  <si>
-    <t>ChIJmdObA76pQjQR0wg8tzukGgY</t>
-  </si>
-  <si>
-    <t>日本60年老店-京昌園燒肉餐廳</t>
-  </si>
-  <si>
-    <t>106台灣台北市大安區延吉街131巷45號</t>
-  </si>
-  <si>
-    <t>02 8773 7122</t>
-  </si>
-  <si>
-    <t>https://k-shoen.com/shops/taipei-yanji/</t>
-  </si>
-  <si>
-    <t>ChIJ07FZWGyrQjQRq0S09w9hKuE</t>
-  </si>
-  <si>
     <t>燒肉燒</t>
   </si>
   <si>
@@ -772,33 +481,6 @@
     <t>ChIJ8e8iyA6pQjQRxy0r7WyXn2M</t>
   </si>
   <si>
-    <t>燒酒烤烤豬丨韓式餐廳丨韓式燒肉丨純淨餐桌(天然豬肉專賣店)</t>
-  </si>
-  <si>
-    <t>106台灣台北市大安區大安路一段51巷22號</t>
-  </si>
-  <si>
-    <t>02 2781 9991</t>
-  </si>
-  <si>
-    <t>ChIJ4XYXOG-rQjQRu8BA0V6_b1U</t>
-  </si>
-  <si>
-    <t>熊一頂級燒肉-西門二店</t>
-  </si>
-  <si>
-    <t>108台灣台北市萬華區西寧南路161號2樓</t>
-  </si>
-  <si>
-    <t>02 2311 2815</t>
-  </si>
-  <si>
-    <t>https://www.mala.com.tw/Home/BrandIndex?verificationCode=2E07D5C6BC66E4B01B3E254E8245FF89</t>
-  </si>
-  <si>
-    <t>ChIJuUyMJpupQjQROEy0e_HHbsc</t>
-  </si>
-  <si>
     <t>大腕燒肉專門店</t>
   </si>
   <si>
@@ -814,48 +496,6 @@
     <t>ChIJqX0G4sSrQjQRYjGrIB6PAcI</t>
   </si>
   <si>
-    <t>燒肉擔當本店 Yakiniku PIC</t>
-  </si>
-  <si>
-    <t>106台灣台北市大安區敦化南路一段161巷52號</t>
-  </si>
-  <si>
-    <t>02 8773 3252</t>
-  </si>
-  <si>
-    <t>https://reurl.cc/mLOXv1</t>
-  </si>
-  <si>
-    <t>ChIJJ9WebIOrQjQRv5mjoqFspr4</t>
-  </si>
-  <si>
-    <t>七輪燒肉-台北店</t>
-  </si>
-  <si>
-    <t>10491台灣台北市中山區八德路二段292號</t>
-  </si>
-  <si>
-    <t>02 8772 7070</t>
-  </si>
-  <si>
-    <t>https://inline.app/booking/-O3mNI_3W3hoVUc7qa6M:inline-live-3/-O3mNIoKQiLLfi_DdYOd</t>
-  </si>
-  <si>
-    <t>ChIJlXggUNmrQjQRZAE0DKRux5I</t>
-  </si>
-  <si>
-    <t>燔之亭 燒肉場-附近燒肉,台北燒肉推薦,燒肉店,無菜單料理,無菜單料理燒肉</t>
-  </si>
-  <si>
-    <t>105台灣台北市松山區延吉街30巷4號</t>
-  </si>
-  <si>
-    <t>02 2579 0809</t>
-  </si>
-  <si>
-    <t>ChIJJy1gHHmpQjQRD7btK9kN0qA</t>
-  </si>
-  <si>
     <t>鉄火燒肉微風北車店</t>
   </si>
   <si>
@@ -877,9 +517,6 @@
     <t>02 2562 1113</t>
   </si>
   <si>
-    <t>https://hatsu.tw/</t>
-  </si>
-  <si>
     <t>ChIJ8bTG3zupQjQR0VqQA9Xrn2w</t>
   </si>
   <si>
@@ -898,49 +535,31 @@
     <t>ChIJmdHk-WGpQjQRu8wJyNGGBbI</t>
   </si>
   <si>
-    <t>Meat Love橡木炭火韓國烤肉 信義店</t>
-  </si>
-  <si>
-    <t>110台灣台北市信義區信義路四段468號</t>
-  </si>
-  <si>
-    <t>02 2729 9488</t>
-  </si>
-  <si>
-    <t>https://meatlove.tw/</t>
-  </si>
-  <si>
-    <t>ChIJy_aVAsqrQjQRLoh-MkT94Vc</t>
-  </si>
-  <si>
-    <t>狠生氣日式燒肉</t>
-  </si>
-  <si>
-    <t>234台灣新北市永和區永和路二段318號</t>
-  </si>
-  <si>
-    <t>02 2928 6385</t>
-  </si>
-  <si>
-    <t>https://0986230906.com/</t>
-  </si>
-  <si>
-    <t>ChIJmb590uqpQjQRyC_J045QtuY</t>
-  </si>
-  <si>
-    <t>京東燒肉專門店忠孝店</t>
-  </si>
-  <si>
-    <t>106台灣台北市大安區忠孝東路四段216巷8弄10號</t>
-  </si>
-  <si>
-    <t>02 8773 8818</t>
-  </si>
-  <si>
-    <t>https://inline.app/booking/-LU0in0Q2sdb0S1PjSZ6:inline-live-2a466/-LU45LSG5AgEbbst9Nzz</t>
-  </si>
-  <si>
-    <t>ChIJbW09UU-rQjQRn56fUza7JkA</t>
+    <t>a0424180511a@gmail.com</t>
+  </si>
+  <si>
+    <t>sitaiyaki@yahoo.com.tw</t>
+  </si>
+  <si>
+    <t>mkt.ylltd@gmail.com</t>
+  </si>
+  <si>
+    <t>https://www.facebook.com/FollowYakiniku</t>
+  </si>
+  <si>
+    <t>marumichi@yummy-life.com</t>
+  </si>
+  <si>
+    <t>yakiniku.vanne@gmail.com</t>
+  </si>
+  <si>
+    <t>https://www.facebook.com/profile.php?id=100063949788428#</t>
+  </si>
+  <si>
+    <t>wowjolihi@gmail.com</t>
+  </si>
+  <si>
+    <t>https://hatsu.tw/contact/</t>
   </si>
 </sst>
 </file>
@@ -1319,7 +938,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:I61"/>
+  <dimension ref="A1:I35"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="29.875" customWidth="1"/>
@@ -1446,16 +1065,16 @@
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>74</v>
+        <v>59</v>
       </c>
       <c r="B5" t="s">
-        <v>75</v>
+        <v>60</v>
       </c>
       <c r="C5" t="s">
-        <v>76</v>
+        <v>61</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>77</v>
+        <v>62</v>
       </c>
       <c r="E5">
         <v>4.5999999999999996</v>
@@ -1464,10 +1083,10 @@
         <v>3929</v>
       </c>
       <c r="G5" t="s">
-        <v>78</v>
+        <v>63</v>
       </c>
       <c r="H5" t="s">
-        <v>79</v>
+        <v>64</v>
       </c>
       <c r="I5" t="s">
         <v>21</v>
@@ -1475,16 +1094,16 @@
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>103</v>
+        <v>74</v>
       </c>
       <c r="B6" t="s">
-        <v>104</v>
+        <v>75</v>
       </c>
       <c r="C6" t="s">
-        <v>105</v>
+        <v>76</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>106</v>
+        <v>77</v>
       </c>
       <c r="E6">
         <v>4.9000000000000004</v>
@@ -1493,10 +1112,10 @@
         <v>10301</v>
       </c>
       <c r="G6" t="s">
-        <v>107</v>
+        <v>78</v>
       </c>
       <c r="H6" t="s">
-        <v>108</v>
+        <v>79</v>
       </c>
       <c r="I6" t="s">
         <v>21</v>
@@ -1504,16 +1123,16 @@
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
-        <v>131</v>
+        <v>85</v>
       </c>
       <c r="B7" t="s">
-        <v>132</v>
+        <v>86</v>
       </c>
       <c r="C7" t="s">
-        <v>133</v>
+        <v>87</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>134</v>
+        <v>88</v>
       </c>
       <c r="E7">
         <v>4.7</v>
@@ -1522,10 +1141,10 @@
         <v>19914</v>
       </c>
       <c r="G7" t="s">
-        <v>135</v>
+        <v>89</v>
       </c>
       <c r="H7" t="s">
-        <v>136</v>
+        <v>90</v>
       </c>
       <c r="I7" t="s">
         <v>21</v>
@@ -1533,16 +1152,16 @@
     </row>
     <row r="8" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
-        <v>161</v>
+        <v>101</v>
       </c>
       <c r="B8" t="s">
-        <v>162</v>
+        <v>102</v>
       </c>
       <c r="C8" t="s">
-        <v>163</v>
+        <v>103</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>164</v>
+        <v>104</v>
       </c>
       <c r="E8">
         <v>4.5999999999999996</v>
@@ -1551,10 +1170,10 @@
         <v>2653</v>
       </c>
       <c r="G8" t="s">
-        <v>165</v>
+        <v>105</v>
       </c>
       <c r="H8" t="s">
-        <v>166</v>
+        <v>106</v>
       </c>
       <c r="I8" t="s">
         <v>21</v>
@@ -1562,16 +1181,16 @@
     </row>
     <row r="9" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
-        <v>189</v>
+        <v>112</v>
       </c>
       <c r="B9" t="s">
-        <v>190</v>
+        <v>113</v>
       </c>
       <c r="C9" t="s">
-        <v>191</v>
+        <v>114</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>192</v>
+        <v>115</v>
       </c>
       <c r="E9">
         <v>4.8</v>
@@ -1580,10 +1199,10 @@
         <v>205</v>
       </c>
       <c r="G9" t="s">
-        <v>193</v>
+        <v>116</v>
       </c>
       <c r="H9" t="s">
-        <v>194</v>
+        <v>117</v>
       </c>
       <c r="I9" t="s">
         <v>21</v>
@@ -1591,16 +1210,16 @@
     </row>
     <row r="10" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
-        <v>195</v>
+        <v>118</v>
       </c>
       <c r="B10" t="s">
-        <v>196</v>
+        <v>119</v>
       </c>
       <c r="C10" t="s">
-        <v>197</v>
+        <v>120</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>198</v>
+        <v>121</v>
       </c>
       <c r="E10">
         <v>4.9000000000000004</v>
@@ -1609,10 +1228,10 @@
         <v>1182</v>
       </c>
       <c r="G10" t="s">
-        <v>199</v>
+        <v>122</v>
       </c>
       <c r="H10" t="s">
-        <v>200</v>
+        <v>123</v>
       </c>
       <c r="I10" t="s">
         <v>21</v>
@@ -1628,7 +1247,7 @@
       <c r="C11" t="s">
         <v>11</v>
       </c>
-      <c r="D11" t="s">
+      <c r="D11" s="2" t="s">
         <v>12</v>
       </c>
       <c r="E11">
@@ -1640,31 +1259,37 @@
       <c r="G11" t="s">
         <v>13</v>
       </c>
+      <c r="H11" t="s">
+        <v>171</v>
+      </c>
       <c r="I11" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="12" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="B12" t="s">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="C12" t="s">
-        <v>36</v>
-      </c>
-      <c r="D12" t="s">
-        <v>37</v>
+        <v>41</v>
+      </c>
+      <c r="D12" s="2" t="s">
+        <v>42</v>
       </c>
       <c r="E12">
-        <v>4.9000000000000004</v>
+        <v>4.7</v>
       </c>
       <c r="F12">
-        <v>19828</v>
+        <v>2575</v>
       </c>
       <c r="G12" t="s">
-        <v>38</v>
+        <v>43</v>
+      </c>
+      <c r="H12" t="s">
+        <v>172</v>
       </c>
       <c r="I12" t="s">
         <v>14</v>
@@ -1672,25 +1297,28 @@
     </row>
     <row r="13" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="B13" t="s">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="C13" t="s">
-        <v>41</v>
-      </c>
-      <c r="D13" t="s">
-        <v>42</v>
+        <v>46</v>
+      </c>
+      <c r="D13" s="2" t="s">
+        <v>47</v>
       </c>
       <c r="E13">
-        <v>4.7</v>
+        <v>4.9000000000000004</v>
       </c>
       <c r="F13">
-        <v>2575</v>
+        <v>11741</v>
       </c>
       <c r="G13" t="s">
-        <v>43</v>
+        <v>48</v>
+      </c>
+      <c r="H13" t="s">
+        <v>173</v>
       </c>
       <c r="I13" t="s">
         <v>14</v>
@@ -1698,25 +1326,28 @@
     </row>
     <row r="14" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
-        <v>44</v>
+        <v>54</v>
       </c>
       <c r="B14" t="s">
-        <v>45</v>
+        <v>55</v>
       </c>
       <c r="C14" t="s">
-        <v>46</v>
-      </c>
-      <c r="D14" t="s">
-        <v>47</v>
+        <v>56</v>
+      </c>
+      <c r="D14" s="2" t="s">
+        <v>57</v>
       </c>
       <c r="E14">
-        <v>4.9000000000000004</v>
+        <v>4.5999999999999996</v>
       </c>
       <c r="F14">
-        <v>11741</v>
+        <v>2457</v>
       </c>
       <c r="G14" t="s">
-        <v>48</v>
+        <v>58</v>
+      </c>
+      <c r="H14" t="s">
+        <v>175</v>
       </c>
       <c r="I14" t="s">
         <v>14</v>
@@ -1724,25 +1355,28 @@
     </row>
     <row r="15" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
-        <v>49</v>
+        <v>91</v>
       </c>
       <c r="B15" t="s">
-        <v>50</v>
+        <v>92</v>
       </c>
       <c r="C15" t="s">
-        <v>51</v>
-      </c>
-      <c r="D15" t="s">
-        <v>52</v>
+        <v>93</v>
+      </c>
+      <c r="D15" s="2" t="s">
+        <v>94</v>
       </c>
       <c r="E15">
-        <v>4.9000000000000004</v>
+        <v>4.4000000000000004</v>
       </c>
       <c r="F15">
-        <v>5060</v>
+        <v>1267</v>
       </c>
       <c r="G15" t="s">
-        <v>53</v>
+        <v>95</v>
+      </c>
+      <c r="H15" t="s">
+        <v>176</v>
       </c>
       <c r="I15" t="s">
         <v>14</v>
@@ -1750,129 +1384,54 @@
     </row>
     <row r="16" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
-        <v>54</v>
+        <v>148</v>
       </c>
       <c r="B16" t="s">
-        <v>55</v>
+        <v>149</v>
       </c>
       <c r="C16" t="s">
-        <v>56</v>
-      </c>
-      <c r="D16" t="s">
-        <v>57</v>
+        <v>150</v>
+      </c>
+      <c r="D16" s="2" t="s">
+        <v>151</v>
       </c>
       <c r="E16">
         <v>4.5999999999999996</v>
       </c>
       <c r="F16">
-        <v>2457</v>
+        <v>8173</v>
       </c>
       <c r="G16" t="s">
-        <v>58</v>
+        <v>152</v>
+      </c>
+      <c r="H16" t="s">
+        <v>178</v>
       </c>
       <c r="I16" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="17" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A17" t="s">
-        <v>59</v>
-      </c>
-      <c r="B17" t="s">
-        <v>60</v>
-      </c>
-      <c r="C17" t="s">
-        <v>61</v>
-      </c>
-      <c r="D17" t="s">
-        <v>62</v>
-      </c>
-      <c r="E17">
-        <v>5</v>
-      </c>
-      <c r="F17">
-        <v>1117</v>
-      </c>
-      <c r="G17" t="s">
-        <v>63</v>
-      </c>
-      <c r="I17" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="18" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A18" t="s">
-        <v>64</v>
-      </c>
-      <c r="B18" t="s">
-        <v>65</v>
-      </c>
-      <c r="C18" t="s">
-        <v>66</v>
-      </c>
-      <c r="D18" t="s">
-        <v>67</v>
-      </c>
-      <c r="E18">
-        <v>4.8</v>
-      </c>
-      <c r="F18">
-        <v>1379</v>
-      </c>
-      <c r="G18" t="s">
-        <v>68</v>
-      </c>
-      <c r="I18" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="19" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A19" t="s">
-        <v>69</v>
-      </c>
-      <c r="B19" t="s">
-        <v>70</v>
-      </c>
-      <c r="C19" t="s">
-        <v>71</v>
-      </c>
-      <c r="D19" t="s">
-        <v>72</v>
-      </c>
-      <c r="E19">
-        <v>4.8</v>
-      </c>
-      <c r="F19">
-        <v>13838</v>
-      </c>
-      <c r="G19" t="s">
-        <v>73</v>
-      </c>
-      <c r="I19" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="20" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
-        <v>80</v>
+        <v>34</v>
       </c>
       <c r="B20" t="s">
-        <v>81</v>
+        <v>35</v>
       </c>
       <c r="C20" t="s">
-        <v>82</v>
+        <v>36</v>
       </c>
       <c r="D20" t="s">
-        <v>52</v>
+        <v>37</v>
       </c>
       <c r="E20">
         <v>4.9000000000000004</v>
       </c>
       <c r="F20">
-        <v>3479</v>
+        <v>19828</v>
       </c>
       <c r="G20" t="s">
-        <v>83</v>
+        <v>38</v>
       </c>
       <c r="I20" t="s">
         <v>14</v>
@@ -1880,25 +1439,25 @@
     </row>
     <row r="21" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
-        <v>84</v>
+        <v>49</v>
       </c>
       <c r="B21" t="s">
-        <v>85</v>
+        <v>50</v>
       </c>
       <c r="C21" t="s">
-        <v>86</v>
+        <v>51</v>
       </c>
       <c r="D21" t="s">
-        <v>87</v>
+        <v>174</v>
       </c>
       <c r="E21">
-        <v>4.7</v>
+        <v>4.9000000000000004</v>
       </c>
       <c r="F21">
-        <v>3593</v>
+        <v>5060</v>
       </c>
       <c r="G21" t="s">
-        <v>88</v>
+        <v>53</v>
       </c>
       <c r="I21" t="s">
         <v>14</v>
@@ -1906,25 +1465,25 @@
     </row>
     <row r="22" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
-        <v>89</v>
+        <v>65</v>
       </c>
       <c r="B22" t="s">
-        <v>90</v>
+        <v>66</v>
       </c>
       <c r="C22" t="s">
-        <v>91</v>
+        <v>67</v>
       </c>
       <c r="D22" t="s">
-        <v>92</v>
+        <v>52</v>
       </c>
       <c r="E22">
-        <v>4.8</v>
+        <v>4.9000000000000004</v>
       </c>
       <c r="F22">
-        <v>222</v>
+        <v>3479</v>
       </c>
       <c r="G22" t="s">
-        <v>93</v>
+        <v>68</v>
       </c>
       <c r="I22" t="s">
         <v>14</v>
@@ -1932,25 +1491,25 @@
     </row>
     <row r="23" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
-        <v>94</v>
+        <v>69</v>
       </c>
       <c r="B23" t="s">
-        <v>95</v>
+        <v>70</v>
       </c>
       <c r="C23" t="s">
-        <v>96</v>
+        <v>71</v>
       </c>
       <c r="D23" t="s">
-        <v>97</v>
+        <v>72</v>
       </c>
       <c r="E23">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="F23">
-        <v>4239</v>
+        <v>3593</v>
       </c>
       <c r="G23" t="s">
-        <v>98</v>
+        <v>73</v>
       </c>
       <c r="I23" t="s">
         <v>14</v>
@@ -1958,25 +1517,25 @@
     </row>
     <row r="24" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
-        <v>99</v>
+        <v>80</v>
       </c>
       <c r="B24" t="s">
-        <v>100</v>
+        <v>81</v>
       </c>
       <c r="C24" t="s">
-        <v>101</v>
+        <v>82</v>
       </c>
       <c r="D24" t="s">
-        <v>47</v>
+        <v>83</v>
       </c>
       <c r="E24">
-        <v>4.9000000000000004</v>
+        <v>4.8</v>
       </c>
       <c r="F24">
-        <v>7298</v>
+        <v>5011</v>
       </c>
       <c r="G24" t="s">
-        <v>102</v>
+        <v>84</v>
       </c>
       <c r="I24" t="s">
         <v>14</v>
@@ -1984,19 +1543,25 @@
     </row>
     <row r="25" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
-        <v>109</v>
+        <v>96</v>
       </c>
       <c r="B25" t="s">
-        <v>110</v>
+        <v>97</v>
+      </c>
+      <c r="C25" t="s">
+        <v>98</v>
+      </c>
+      <c r="D25" t="s">
+        <v>99</v>
       </c>
       <c r="E25">
-        <v>5</v>
+        <v>4.5999999999999996</v>
       </c>
       <c r="F25">
-        <v>37</v>
+        <v>468</v>
       </c>
       <c r="G25" t="s">
-        <v>111</v>
+        <v>100</v>
       </c>
       <c r="I25" t="s">
         <v>14</v>
@@ -2004,22 +1569,25 @@
     </row>
     <row r="26" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
-        <v>112</v>
+        <v>107</v>
       </c>
       <c r="B26" t="s">
-        <v>113</v>
+        <v>108</v>
       </c>
       <c r="C26" t="s">
-        <v>114</v>
+        <v>109</v>
+      </c>
+      <c r="D26" t="s">
+        <v>110</v>
       </c>
       <c r="E26">
         <v>4.8</v>
       </c>
       <c r="F26">
-        <v>2157</v>
+        <v>3889</v>
       </c>
       <c r="G26" t="s">
-        <v>115</v>
+        <v>111</v>
       </c>
       <c r="I26" t="s">
         <v>14</v>
@@ -2027,25 +1595,25 @@
     </row>
     <row r="27" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
-        <v>116</v>
+        <v>124</v>
       </c>
       <c r="B27" t="s">
-        <v>117</v>
+        <v>125</v>
       </c>
       <c r="C27" t="s">
-        <v>118</v>
+        <v>126</v>
       </c>
       <c r="D27" t="s">
-        <v>119</v>
+        <v>177</v>
       </c>
       <c r="E27">
         <v>4.8</v>
       </c>
       <c r="F27">
-        <v>4887</v>
+        <v>6393</v>
       </c>
       <c r="G27" t="s">
-        <v>120</v>
+        <v>127</v>
       </c>
       <c r="I27" t="s">
         <v>14</v>
@@ -2053,25 +1621,25 @@
     </row>
     <row r="28" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
-        <v>121</v>
+        <v>128</v>
       </c>
       <c r="B28" t="s">
-        <v>122</v>
+        <v>129</v>
       </c>
       <c r="C28" t="s">
-        <v>123</v>
+        <v>130</v>
       </c>
       <c r="D28" t="s">
-        <v>124</v>
+        <v>131</v>
       </c>
       <c r="E28">
-        <v>4.9000000000000004</v>
+        <v>4.5999999999999996</v>
       </c>
       <c r="F28">
-        <v>1179</v>
+        <v>980</v>
       </c>
       <c r="G28" t="s">
-        <v>125</v>
+        <v>132</v>
       </c>
       <c r="I28" t="s">
         <v>14</v>
@@ -2079,25 +1647,25 @@
     </row>
     <row r="29" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
-        <v>126</v>
+        <v>133</v>
       </c>
       <c r="B29" t="s">
-        <v>127</v>
+        <v>134</v>
       </c>
       <c r="C29" t="s">
-        <v>128</v>
+        <v>135</v>
       </c>
       <c r="D29" t="s">
-        <v>129</v>
+        <v>136</v>
       </c>
       <c r="E29">
         <v>4.8</v>
       </c>
       <c r="F29">
-        <v>5011</v>
+        <v>4876</v>
       </c>
       <c r="G29" t="s">
-        <v>130</v>
+        <v>137</v>
       </c>
       <c r="I29" t="s">
         <v>14</v>
@@ -2105,25 +1673,25 @@
     </row>
     <row r="30" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="B30" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="C30" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="D30" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="E30">
-        <v>4.4000000000000004</v>
+        <v>4.5999999999999996</v>
       </c>
       <c r="F30">
-        <v>1267</v>
+        <v>1626</v>
       </c>
       <c r="G30" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="I30" t="s">
         <v>14</v>
@@ -2131,25 +1699,25 @@
     </row>
     <row r="31" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="B31" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="C31" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="D31" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="E31">
-        <v>4.7</v>
+        <v>4.5</v>
       </c>
       <c r="F31">
-        <v>872</v>
+        <v>933</v>
       </c>
       <c r="G31" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="I31" t="s">
         <v>14</v>
@@ -2157,25 +1725,25 @@
     </row>
     <row r="32" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
-        <v>147</v>
+        <v>153</v>
       </c>
       <c r="B32" t="s">
-        <v>148</v>
+        <v>154</v>
       </c>
       <c r="C32" t="s">
-        <v>149</v>
+        <v>155</v>
       </c>
       <c r="D32" t="s">
-        <v>150</v>
+        <v>156</v>
       </c>
       <c r="E32">
-        <v>4.5999999999999996</v>
+        <v>4.3</v>
       </c>
       <c r="F32">
-        <v>468</v>
+        <v>2337</v>
       </c>
       <c r="G32" t="s">
-        <v>151</v>
+        <v>157</v>
       </c>
       <c r="I32" t="s">
         <v>14</v>
@@ -2183,25 +1751,22 @@
     </row>
     <row r="33" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
-        <v>152</v>
+        <v>158</v>
       </c>
       <c r="B33" t="s">
-        <v>153</v>
-      </c>
-      <c r="C33" t="s">
-        <v>154</v>
+        <v>159</v>
       </c>
       <c r="D33" t="s">
-        <v>155</v>
+        <v>160</v>
       </c>
       <c r="E33">
-        <v>4.8</v>
+        <v>4.5999999999999996</v>
       </c>
       <c r="F33">
-        <v>19391</v>
+        <v>5376</v>
       </c>
       <c r="G33" t="s">
-        <v>156</v>
+        <v>161</v>
       </c>
       <c r="I33" t="s">
         <v>14</v>
@@ -2209,25 +1774,25 @@
     </row>
     <row r="34" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
-        <v>157</v>
+        <v>162</v>
       </c>
       <c r="B34" t="s">
-        <v>158</v>
+        <v>163</v>
       </c>
       <c r="C34" t="s">
-        <v>159</v>
+        <v>164</v>
       </c>
       <c r="D34" t="s">
-        <v>155</v>
+        <v>179</v>
       </c>
       <c r="E34">
-        <v>4.8</v>
+        <v>4.5999999999999996</v>
       </c>
       <c r="F34">
-        <v>7915</v>
+        <v>1364</v>
       </c>
       <c r="G34" t="s">
-        <v>160</v>
+        <v>165</v>
       </c>
       <c r="I34" t="s">
         <v>14</v>
@@ -2235,19 +1800,22 @@
     </row>
     <row r="35" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
+        <v>166</v>
+      </c>
+      <c r="B35" t="s">
         <v>167</v>
       </c>
-      <c r="B35" t="s">
+      <c r="C35" t="s">
         <v>168</v>
       </c>
-      <c r="C35" t="s">
+      <c r="D35" t="s">
         <v>169</v>
       </c>
       <c r="E35">
         <v>4.5999999999999996</v>
       </c>
       <c r="F35">
-        <v>5858</v>
+        <v>4600</v>
       </c>
       <c r="G35" t="s">
         <v>170</v>
@@ -2256,673 +1824,9 @@
         <v>14</v>
       </c>
     </row>
-    <row r="36" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A36" t="s">
-        <v>171</v>
-      </c>
-      <c r="B36" t="s">
-        <v>172</v>
-      </c>
-      <c r="C36" t="s">
-        <v>173</v>
-      </c>
-      <c r="D36" t="s">
-        <v>174</v>
-      </c>
-      <c r="E36">
-        <v>4.7</v>
-      </c>
-      <c r="F36">
-        <v>9982</v>
-      </c>
-      <c r="G36" t="s">
-        <v>175</v>
-      </c>
-      <c r="I36" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="37" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A37" t="s">
-        <v>176</v>
-      </c>
-      <c r="B37" t="s">
-        <v>177</v>
-      </c>
-      <c r="C37" t="s">
-        <v>178</v>
-      </c>
-      <c r="D37" t="s">
-        <v>179</v>
-      </c>
-      <c r="E37">
-        <v>4.8</v>
-      </c>
-      <c r="F37">
-        <v>3889</v>
-      </c>
-      <c r="G37" t="s">
-        <v>180</v>
-      </c>
-      <c r="I37" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="38" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A38" t="s">
-        <v>181</v>
-      </c>
-      <c r="B38" t="s">
-        <v>182</v>
-      </c>
-      <c r="C38" t="s">
-        <v>183</v>
-      </c>
-      <c r="D38" t="s">
-        <v>124</v>
-      </c>
-      <c r="E38">
-        <v>4.8</v>
-      </c>
-      <c r="F38">
-        <v>2860</v>
-      </c>
-      <c r="G38" t="s">
-        <v>184</v>
-      </c>
-      <c r="I38" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="39" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A39" t="s">
-        <v>185</v>
-      </c>
-      <c r="B39" t="s">
-        <v>186</v>
-      </c>
-      <c r="C39" t="s">
-        <v>187</v>
-      </c>
-      <c r="D39" t="s">
-        <v>124</v>
-      </c>
-      <c r="E39">
-        <v>4.9000000000000004</v>
-      </c>
-      <c r="F39">
-        <v>1904</v>
-      </c>
-      <c r="G39" t="s">
-        <v>188</v>
-      </c>
-      <c r="I39" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="40" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A40" t="s">
-        <v>201</v>
-      </c>
-      <c r="B40" t="s">
-        <v>202</v>
-      </c>
-      <c r="C40" t="s">
-        <v>203</v>
-      </c>
-      <c r="D40" t="s">
-        <v>204</v>
-      </c>
-      <c r="E40">
-        <v>4.8</v>
-      </c>
-      <c r="F40">
-        <v>6393</v>
-      </c>
-      <c r="G40" t="s">
-        <v>205</v>
-      </c>
-      <c r="I40" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="41" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A41" t="s">
-        <v>206</v>
-      </c>
-      <c r="B41" t="s">
-        <v>207</v>
-      </c>
-      <c r="C41" t="s">
-        <v>208</v>
-      </c>
-      <c r="D41" t="s">
-        <v>209</v>
-      </c>
-      <c r="E41">
-        <v>4.5999999999999996</v>
-      </c>
-      <c r="F41">
-        <v>980</v>
-      </c>
-      <c r="G41" t="s">
-        <v>210</v>
-      </c>
-      <c r="I41" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="42" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A42" t="s">
-        <v>211</v>
-      </c>
-      <c r="B42" t="s">
-        <v>212</v>
-      </c>
-      <c r="C42" t="s">
-        <v>213</v>
-      </c>
-      <c r="D42" t="s">
-        <v>214</v>
-      </c>
-      <c r="E42">
-        <v>4.8</v>
-      </c>
-      <c r="F42">
-        <v>4876</v>
-      </c>
-      <c r="G42" t="s">
-        <v>215</v>
-      </c>
-      <c r="I42" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="43" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A43" t="s">
-        <v>216</v>
-      </c>
-      <c r="B43" t="s">
-        <v>217</v>
-      </c>
-      <c r="C43" t="s">
-        <v>218</v>
-      </c>
-      <c r="D43" t="s">
-        <v>219</v>
-      </c>
-      <c r="E43">
-        <v>4.9000000000000004</v>
-      </c>
-      <c r="F43">
-        <v>530</v>
-      </c>
-      <c r="G43" t="s">
-        <v>220</v>
-      </c>
-      <c r="I43" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="44" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A44" t="s">
-        <v>221</v>
-      </c>
-      <c r="B44" t="s">
-        <v>222</v>
-      </c>
-      <c r="C44" t="s">
-        <v>223</v>
-      </c>
-      <c r="E44">
-        <v>4.5999999999999996</v>
-      </c>
-      <c r="F44">
-        <v>1770</v>
-      </c>
-      <c r="G44" t="s">
-        <v>224</v>
-      </c>
-      <c r="I44" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="45" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A45" t="s">
-        <v>225</v>
-      </c>
-      <c r="B45" t="s">
-        <v>226</v>
-      </c>
-      <c r="C45" t="s">
-        <v>227</v>
-      </c>
-      <c r="D45" t="s">
-        <v>228</v>
-      </c>
-      <c r="E45">
-        <v>4.5999999999999996</v>
-      </c>
-      <c r="F45">
-        <v>1626</v>
-      </c>
-      <c r="G45" t="s">
-        <v>229</v>
-      </c>
-      <c r="I45" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="46" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A46" t="s">
-        <v>230</v>
-      </c>
-      <c r="B46" t="s">
-        <v>231</v>
-      </c>
-      <c r="C46" t="s">
-        <v>232</v>
-      </c>
-      <c r="D46" t="s">
-        <v>233</v>
-      </c>
-      <c r="E46">
-        <v>4.7</v>
-      </c>
-      <c r="F46">
-        <v>1564</v>
-      </c>
-      <c r="G46" t="s">
-        <v>234</v>
-      </c>
-      <c r="I46" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="47" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A47" t="s">
-        <v>235</v>
-      </c>
-      <c r="B47" t="s">
-        <v>236</v>
-      </c>
-      <c r="C47" t="s">
-        <v>237</v>
-      </c>
-      <c r="D47" t="s">
-        <v>238</v>
-      </c>
-      <c r="E47">
-        <v>4.5</v>
-      </c>
-      <c r="F47">
-        <v>1310</v>
-      </c>
-      <c r="G47" t="s">
-        <v>239</v>
-      </c>
-      <c r="I47" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="48" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A48" t="s">
-        <v>240</v>
-      </c>
-      <c r="B48" t="s">
-        <v>241</v>
-      </c>
-      <c r="C48" t="s">
-        <v>242</v>
-      </c>
-      <c r="D48" t="s">
-        <v>243</v>
-      </c>
-      <c r="E48">
-        <v>4.5</v>
-      </c>
-      <c r="F48">
-        <v>933</v>
-      </c>
-      <c r="G48" t="s">
-        <v>244</v>
-      </c>
-      <c r="I48" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="49" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A49" t="s">
-        <v>245</v>
-      </c>
-      <c r="B49" t="s">
-        <v>246</v>
-      </c>
-      <c r="C49" t="s">
-        <v>247</v>
-      </c>
-      <c r="D49" t="s">
-        <v>248</v>
-      </c>
-      <c r="E49">
-        <v>4.5999999999999996</v>
-      </c>
-      <c r="F49">
-        <v>8173</v>
-      </c>
-      <c r="G49" t="s">
-        <v>249</v>
-      </c>
-      <c r="I49" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="50" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A50" t="s">
-        <v>250</v>
-      </c>
-      <c r="B50" t="s">
-        <v>251</v>
-      </c>
-      <c r="C50" t="s">
-        <v>252</v>
-      </c>
-      <c r="E50">
-        <v>4.7</v>
-      </c>
-      <c r="F50">
-        <v>1493</v>
-      </c>
-      <c r="G50" t="s">
-        <v>253</v>
-      </c>
-      <c r="I50" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="51" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A51" t="s">
-        <v>254</v>
-      </c>
-      <c r="B51" t="s">
-        <v>255</v>
-      </c>
-      <c r="C51" t="s">
-        <v>256</v>
-      </c>
-      <c r="D51" t="s">
-        <v>257</v>
-      </c>
-      <c r="E51">
-        <v>4.7</v>
-      </c>
-      <c r="F51">
-        <v>8562</v>
-      </c>
-      <c r="G51" t="s">
-        <v>258</v>
-      </c>
-      <c r="I51" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="52" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A52" t="s">
-        <v>259</v>
-      </c>
-      <c r="B52" t="s">
-        <v>260</v>
-      </c>
-      <c r="C52" t="s">
-        <v>261</v>
-      </c>
-      <c r="D52" t="s">
-        <v>262</v>
-      </c>
-      <c r="E52">
-        <v>4.3</v>
-      </c>
-      <c r="F52">
-        <v>2337</v>
-      </c>
-      <c r="G52" t="s">
-        <v>263</v>
-      </c>
-      <c r="I52" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="53" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A53" t="s">
-        <v>264</v>
-      </c>
-      <c r="B53" t="s">
-        <v>265</v>
-      </c>
-      <c r="C53" t="s">
-        <v>266</v>
-      </c>
-      <c r="D53" t="s">
-        <v>267</v>
-      </c>
-      <c r="E53">
-        <v>4.5</v>
-      </c>
-      <c r="F53">
-        <v>426</v>
-      </c>
-      <c r="G53" t="s">
-        <v>268</v>
-      </c>
-      <c r="I53" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="54" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A54" t="s">
-        <v>269</v>
-      </c>
-      <c r="B54" t="s">
-        <v>270</v>
-      </c>
-      <c r="C54" t="s">
-        <v>271</v>
-      </c>
-      <c r="D54" t="s">
-        <v>272</v>
-      </c>
-      <c r="E54">
-        <v>4.5999999999999996</v>
-      </c>
-      <c r="F54">
-        <v>1211</v>
-      </c>
-      <c r="G54" t="s">
-        <v>273</v>
-      </c>
-      <c r="I54" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="55" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A55" t="s">
-        <v>274</v>
-      </c>
-      <c r="B55" t="s">
-        <v>275</v>
-      </c>
-      <c r="C55" t="s">
-        <v>276</v>
-      </c>
-      <c r="E55">
-        <v>4.8</v>
-      </c>
-      <c r="F55">
-        <v>289</v>
-      </c>
-      <c r="G55" t="s">
-        <v>277</v>
-      </c>
-      <c r="I55" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="56" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A56" t="s">
-        <v>278</v>
-      </c>
-      <c r="B56" t="s">
-        <v>279</v>
-      </c>
-      <c r="D56" t="s">
-        <v>280</v>
-      </c>
-      <c r="E56">
-        <v>4.5999999999999996</v>
-      </c>
-      <c r="F56">
-        <v>5376</v>
-      </c>
-      <c r="G56" t="s">
-        <v>281</v>
-      </c>
-      <c r="I56" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="57" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A57" t="s">
-        <v>282</v>
-      </c>
-      <c r="B57" t="s">
-        <v>283</v>
-      </c>
-      <c r="C57" t="s">
-        <v>284</v>
-      </c>
-      <c r="D57" t="s">
-        <v>285</v>
-      </c>
-      <c r="E57">
-        <v>4.5999999999999996</v>
-      </c>
-      <c r="F57">
-        <v>1364</v>
-      </c>
-      <c r="G57" t="s">
-        <v>286</v>
-      </c>
-      <c r="I57" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="58" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A58" t="s">
-        <v>287</v>
-      </c>
-      <c r="B58" t="s">
-        <v>288</v>
-      </c>
-      <c r="C58" t="s">
-        <v>289</v>
-      </c>
-      <c r="D58" t="s">
-        <v>290</v>
-      </c>
-      <c r="E58">
-        <v>4.5999999999999996</v>
-      </c>
-      <c r="F58">
-        <v>4600</v>
-      </c>
-      <c r="G58" t="s">
-        <v>291</v>
-      </c>
-      <c r="I58" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="59" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A59" t="s">
-        <v>292</v>
-      </c>
-      <c r="B59" t="s">
-        <v>293</v>
-      </c>
-      <c r="C59" t="s">
-        <v>294</v>
-      </c>
-      <c r="D59" t="s">
-        <v>295</v>
-      </c>
-      <c r="E59">
-        <v>4.4000000000000004</v>
-      </c>
-      <c r="F59">
-        <v>4136</v>
-      </c>
-      <c r="G59" t="s">
-        <v>296</v>
-      </c>
-      <c r="I59" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="60" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A60" t="s">
-        <v>297</v>
-      </c>
-      <c r="B60" t="s">
-        <v>298</v>
-      </c>
-      <c r="C60" t="s">
-        <v>299</v>
-      </c>
-      <c r="D60" t="s">
-        <v>300</v>
-      </c>
-      <c r="E60">
-        <v>4.3</v>
-      </c>
-      <c r="F60">
-        <v>4207</v>
-      </c>
-      <c r="G60" t="s">
-        <v>301</v>
-      </c>
-      <c r="I60" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="61" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A61" t="s">
-        <v>302</v>
-      </c>
-      <c r="B61" t="s">
-        <v>303</v>
-      </c>
-      <c r="C61" t="s">
-        <v>304</v>
-      </c>
-      <c r="D61" t="s">
-        <v>305</v>
-      </c>
-      <c r="E61">
-        <v>4.4000000000000004</v>
-      </c>
-      <c r="F61">
-        <v>638</v>
-      </c>
-      <c r="G61" t="s">
-        <v>306</v>
-      </c>
-      <c r="I61" t="s">
-        <v>14</v>
-      </c>
-    </row>
   </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:I61">
-    <sortCondition ref="I2:I61"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:I35">
+    <sortCondition ref="I2:I35"/>
   </sortState>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
